--- a/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_lemon.xlsx
+++ b/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_lemon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\Poincare beams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EB2211-310D-4924-82EB-3762D1969CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AFE557-A3F0-4BA5-BE3F-3177368CA5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="2955" windowWidth="13725" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="645" windowWidth="12630" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="13">
   <si>
     <t>Beam A</t>
   </si>
@@ -64,15 +64,30 @@
   <si>
     <t>HG</t>
   </si>
+  <si>
+    <t>HG10</t>
+  </si>
+  <si>
+    <t>HG01</t>
+  </si>
+  <si>
+    <t>HG00</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -404,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D60"/>
+  <dimension ref="A2:D90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
@@ -414,8 +429,8 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>49</v>
+      <c r="B2" t="s">
+        <v>10</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -428,8 +443,8 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3">
-        <v>49</v>
+      <c r="B3" t="s">
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -442,50 +457,50 @@
       <c r="A4" t="s">
         <v>1</v>
       </c>
-      <c r="B4">
-        <v>49</v>
+      <c r="B4" t="s">
+        <v>10</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>33.851999999999997</v>
+        <v>33.932000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
-      <c r="B5">
-        <v>49</v>
+      <c r="B5" t="s">
+        <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>12.596500000000001</v>
+        <v>12.5975</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B6">
-        <v>49</v>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>98.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
-      <c r="B7">
-        <v>49</v>
+      <c r="B7" t="s">
+        <v>10</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -498,8 +513,8 @@
       <c r="A8" t="s">
         <v>2</v>
       </c>
-      <c r="B8">
-        <v>49</v>
+      <c r="B8" t="s">
+        <v>10</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -512,22 +527,22 @@
       <c r="A9" t="s">
         <v>0</v>
       </c>
-      <c r="B9">
-        <v>49</v>
+      <c r="B9" t="s">
+        <v>10</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
-      <c r="B10">
-        <v>49</v>
+      <c r="B10" t="s">
+        <v>10</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -540,23 +555,22 @@
       <c r="A11" t="s">
         <v>2</v>
       </c>
-      <c r="B11">
-        <v>49</v>
+      <c r="B11" t="s">
+        <v>10</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11">
-        <f>0.75*0.4</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
-      <c r="B12">
-        <v>49</v>
+      <c r="B12" t="s">
+        <v>10</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
@@ -569,8 +583,8 @@
       <c r="A13" t="s">
         <v>0</v>
       </c>
-      <c r="B13">
-        <v>49</v>
+      <c r="B13" t="s">
+        <v>10</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
@@ -583,8 +597,8 @@
       <c r="A14" t="s">
         <v>1</v>
       </c>
-      <c r="B14">
-        <v>49</v>
+      <c r="B14" t="s">
+        <v>10</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
@@ -597,8 +611,8 @@
       <c r="A15" t="s">
         <v>1</v>
       </c>
-      <c r="B15">
-        <v>49</v>
+      <c r="B15" t="s">
+        <v>10</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
@@ -611,8 +625,8 @@
       <c r="A17" t="s">
         <v>0</v>
       </c>
-      <c r="B17">
-        <v>49</v>
+      <c r="B17" t="s">
+        <v>11</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
@@ -625,8 +639,8 @@
       <c r="A18" t="s">
         <v>0</v>
       </c>
-      <c r="B18">
-        <v>49</v>
+      <c r="B18" t="s">
+        <v>11</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
@@ -639,50 +653,50 @@
       <c r="A19" t="s">
         <v>1</v>
       </c>
-      <c r="B19">
-        <v>49</v>
+      <c r="B19" t="s">
+        <v>11</v>
       </c>
       <c r="C19" t="s">
         <v>3</v>
       </c>
       <c r="D19">
-        <v>33.851999999999997</v>
+        <v>33.932000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
-      <c r="B20">
-        <v>49</v>
+      <c r="B20" t="s">
+        <v>11</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
       </c>
       <c r="D20">
-        <v>12.596500000000001</v>
+        <v>12.5975</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>0</v>
       </c>
-      <c r="B21">
-        <v>49</v>
+      <c r="B21" t="s">
+        <v>11</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
       <c r="D21">
-        <v>98.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1</v>
       </c>
-      <c r="B22">
-        <v>49</v>
+      <c r="B22" t="s">
+        <v>11</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -695,36 +709,36 @@
       <c r="A23" t="s">
         <v>2</v>
       </c>
-      <c r="B23">
-        <v>49</v>
+      <c r="B23" t="s">
+        <v>11</v>
       </c>
       <c r="C23" t="s">
         <v>6</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>0</v>
       </c>
-      <c r="B24">
-        <v>49</v>
+      <c r="B24" t="s">
+        <v>11</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
       </c>
       <c r="D24">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
-      <c r="B25">
-        <v>49</v>
+      <c r="B25" t="s">
+        <v>11</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
@@ -737,22 +751,22 @@
       <c r="A26" t="s">
         <v>2</v>
       </c>
-      <c r="B26">
-        <v>49</v>
+      <c r="B26" t="s">
+        <v>11</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>0</v>
       </c>
-      <c r="B27">
-        <v>49</v>
+      <c r="B27" t="s">
+        <v>11</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -765,22 +779,22 @@
       <c r="A28" t="s">
         <v>0</v>
       </c>
-      <c r="B28">
-        <v>49</v>
+      <c r="B28" t="s">
+        <v>11</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1</v>
       </c>
-      <c r="B29">
-        <v>49</v>
+      <c r="B29" t="s">
+        <v>11</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -793,8 +807,8 @@
       <c r="A30" t="s">
         <v>1</v>
       </c>
-      <c r="B30">
-        <v>49</v>
+      <c r="B30" t="s">
+        <v>11</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -807,8 +821,8 @@
       <c r="A32" t="s">
         <v>0</v>
       </c>
-      <c r="B32">
-        <v>49</v>
+      <c r="B32" t="s">
+        <v>12</v>
       </c>
       <c r="C32" t="s">
         <v>3</v>
@@ -821,8 +835,8 @@
       <c r="A33" t="s">
         <v>0</v>
       </c>
-      <c r="B33">
-        <v>49</v>
+      <c r="B33" t="s">
+        <v>12</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
@@ -835,50 +849,50 @@
       <c r="A34" t="s">
         <v>1</v>
       </c>
-      <c r="B34">
-        <v>49</v>
+      <c r="B34" t="s">
+        <v>12</v>
       </c>
       <c r="C34" t="s">
         <v>3</v>
       </c>
       <c r="D34">
-        <v>33.851999999999997</v>
+        <v>33.932000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1</v>
       </c>
-      <c r="B35">
-        <v>49</v>
+      <c r="B35" t="s">
+        <v>12</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
       </c>
       <c r="D35">
-        <v>12.596500000000001</v>
+        <v>12.5975</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
-      <c r="B36">
-        <v>49</v>
+      <c r="B36" t="s">
+        <v>12</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
       </c>
       <c r="D36">
-        <v>98.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1</v>
       </c>
-      <c r="B37">
-        <v>49</v>
+      <c r="B37" t="s">
+        <v>12</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -891,64 +905,64 @@
       <c r="A38" t="s">
         <v>2</v>
       </c>
-      <c r="B38">
-        <v>49</v>
+      <c r="B38" t="s">
+        <v>12</v>
       </c>
       <c r="C38" t="s">
         <v>6</v>
       </c>
       <c r="D38">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>0</v>
       </c>
-      <c r="B39">
-        <v>49</v>
+      <c r="B39" t="s">
+        <v>12</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1</v>
       </c>
-      <c r="B40">
-        <v>49</v>
+      <c r="B40" t="s">
+        <v>12</v>
       </c>
       <c r="C40" t="s">
         <v>7</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>2</v>
       </c>
-      <c r="B41">
-        <v>49</v>
+      <c r="B41" t="s">
+        <v>12</v>
       </c>
       <c r="C41" t="s">
         <v>8</v>
       </c>
       <c r="D41">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>0</v>
       </c>
-      <c r="B42">
-        <v>49</v>
+      <c r="B42" t="s">
+        <v>12</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
@@ -961,8 +975,8 @@
       <c r="A43" t="s">
         <v>0</v>
       </c>
-      <c r="B43">
-        <v>49</v>
+      <c r="B43" t="s">
+        <v>12</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
@@ -975,22 +989,22 @@
       <c r="A44" t="s">
         <v>1</v>
       </c>
-      <c r="B44">
-        <v>49</v>
+      <c r="B44" t="s">
+        <v>12</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1</v>
       </c>
-      <c r="B45">
-        <v>49</v>
+      <c r="B45" t="s">
+        <v>12</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
@@ -1003,8 +1017,8 @@
       <c r="A47" t="s">
         <v>0</v>
       </c>
-      <c r="B47">
-        <v>49</v>
+      <c r="B47" t="s">
+        <v>10</v>
       </c>
       <c r="C47" t="s">
         <v>3</v>
@@ -1017,8 +1031,8 @@
       <c r="A48" t="s">
         <v>0</v>
       </c>
-      <c r="B48">
-        <v>49</v>
+      <c r="B48" t="s">
+        <v>10</v>
       </c>
       <c r="C48" t="s">
         <v>4</v>
@@ -1031,50 +1045,50 @@
       <c r="A49" t="s">
         <v>1</v>
       </c>
-      <c r="B49">
-        <v>49</v>
+      <c r="B49" t="s">
+        <v>10</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
       </c>
       <c r="D49">
-        <v>33.851999999999997</v>
+        <v>33.932000000000002</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1</v>
       </c>
-      <c r="B50">
-        <v>49</v>
+      <c r="B50" t="s">
+        <v>10</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
       </c>
       <c r="D50">
-        <v>12.596500000000001</v>
+        <v>12.5975</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>0</v>
       </c>
-      <c r="B51">
-        <v>49</v>
+      <c r="B51" t="s">
+        <v>10</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
       </c>
       <c r="D51">
-        <v>98.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1</v>
       </c>
-      <c r="B52">
-        <v>49</v>
+      <c r="B52" t="s">
+        <v>10</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -1087,22 +1101,22 @@
       <c r="A53" t="s">
         <v>2</v>
       </c>
-      <c r="B53">
-        <v>49</v>
+      <c r="B53" t="s">
+        <v>10</v>
       </c>
       <c r="C53" t="s">
         <v>6</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>0</v>
       </c>
-      <c r="B54">
-        <v>49</v>
+      <c r="B54" t="s">
+        <v>10</v>
       </c>
       <c r="C54" t="s">
         <v>7</v>
@@ -1115,8 +1129,8 @@
       <c r="A55" t="s">
         <v>1</v>
       </c>
-      <c r="B55">
-        <v>49</v>
+      <c r="B55" t="s">
+        <v>10</v>
       </c>
       <c r="C55" t="s">
         <v>7</v>
@@ -1129,22 +1143,22 @@
       <c r="A56" t="s">
         <v>2</v>
       </c>
-      <c r="B56">
-        <v>49</v>
+      <c r="B56" t="s">
+        <v>10</v>
       </c>
       <c r="C56" t="s">
         <v>8</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>0</v>
       </c>
-      <c r="B57">
-        <v>49</v>
+      <c r="B57" t="s">
+        <v>10</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
@@ -1157,8 +1171,8 @@
       <c r="A58" t="s">
         <v>0</v>
       </c>
-      <c r="B58">
-        <v>49</v>
+      <c r="B58" t="s">
+        <v>10</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
@@ -1171,22 +1185,22 @@
       <c r="A59" t="s">
         <v>1</v>
       </c>
-      <c r="B59">
-        <v>49</v>
+      <c r="B59" t="s">
+        <v>10</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1</v>
       </c>
-      <c r="B60">
-        <v>49</v>
+      <c r="B60" t="s">
+        <v>10</v>
       </c>
       <c r="C60" t="s">
         <v>9</v>
@@ -1195,7 +1209,400 @@
         <v>0</v>
       </c>
     </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62">
+        <v>10.66666666666667</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63">
+        <v>12.77777777777778</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1</v>
+      </c>
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>33.932000000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65">
+        <v>12.5975</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>2</v>
+      </c>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1</v>
+      </c>
+      <c r="B74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1</v>
+      </c>
+      <c r="B75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77">
+        <v>10.66666666666667</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78">
+        <v>12.77777777777778</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>1</v>
+      </c>
+      <c r="B79" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79">
+        <v>33.932000000000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>1</v>
+      </c>
+      <c r="B80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80">
+        <v>12.5975</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>1</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B84" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>0</v>
+      </c>
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1</v>
+      </c>
+      <c r="B89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1</v>
+      </c>
+      <c r="B90" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_lemon.xlsx
+++ b/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_lemon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\Poincare beams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AFE557-A3F0-4BA5-BE3F-3177368CA5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEBA2D5-C34D-4E9C-B302-F0866C1FFFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="645" windowWidth="12630" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10980" yWindow="945" windowWidth="12630" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -464,7 +464,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>33.932000000000002</v>
+        <v>33.991999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -478,7 +478,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>12.5975</v>
+        <v>12.612</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -562,7 +562,7 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -660,7 +660,7 @@
         <v>3</v>
       </c>
       <c r="D19">
-        <v>33.932000000000002</v>
+        <v>33.991999999999997</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -674,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="D20">
-        <v>12.5975</v>
+        <v>12.612</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -716,7 +716,7 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -758,7 +758,8 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <f>0.7*0.8</f>
+        <v>0.55999999999999994</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -856,7 +857,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>33.932000000000002</v>
+        <v>33.991999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -870,7 +871,7 @@
         <v>4</v>
       </c>
       <c r="D35">
-        <v>12.5975</v>
+        <v>12.612</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -954,7 +955,8 @@
         <v>8</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <f>0.7*0.8</f>
+        <v>0.55999999999999994</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1052,7 +1054,7 @@
         <v>3</v>
       </c>
       <c r="D49">
-        <v>33.932000000000002</v>
+        <v>33.799999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1066,7 +1068,7 @@
         <v>4</v>
       </c>
       <c r="D50">
-        <v>12.5975</v>
+        <v>12.612</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1108,7 +1110,7 @@
         <v>6</v>
       </c>
       <c r="D53">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1150,7 +1152,8 @@
         <v>8</v>
       </c>
       <c r="D56">
-        <v>1.1499999999999999</v>
+        <f>1.15*0.8</f>
+        <v>0.91999999999999993</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1248,7 +1251,7 @@
         <v>3</v>
       </c>
       <c r="D64">
-        <v>33.932000000000002</v>
+        <v>33.799999999999997</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1262,7 +1265,7 @@
         <v>4</v>
       </c>
       <c r="D65">
-        <v>12.5975</v>
+        <v>12.612</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1304,7 +1307,7 @@
         <v>6</v>
       </c>
       <c r="D68">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1346,7 +1349,8 @@
         <v>8</v>
       </c>
       <c r="D71">
-        <v>1.1499999999999999</v>
+        <f>1.15*0.8</f>
+        <v>0.91999999999999993</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1444,7 +1448,7 @@
         <v>3</v>
       </c>
       <c r="D79">
-        <v>33.932000000000002</v>
+        <v>33.799999999999997</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1458,7 +1462,7 @@
         <v>4</v>
       </c>
       <c r="D80">
-        <v>12.5975</v>
+        <v>12.612</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1542,7 +1546,7 @@
         <v>8</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">

--- a/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_lemon.xlsx
+++ b/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_lemon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\Poincare beams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A061DA-FBF0-4B83-BBA9-128E3629C481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261782C9-1244-478C-87A5-B741236249AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11325" yWindow="1290" windowWidth="12630" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20400" yWindow="6690" windowWidth="7485" windowHeight="8670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -478,7 +478,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>33.991999999999997</v>
+        <v>33.911999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -492,7 +492,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1">
-        <v>12.612</v>
+        <v>12.569000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -680,7 +680,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>33.991999999999997</v>
+        <v>33.911999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -694,7 +694,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>12.612</v>
+        <v>12.569000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,7 +882,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1">
-        <v>33.991999999999997</v>
+        <v>33.911999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -896,7 +896,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="1">
-        <v>12.612</v>
+        <v>12.569000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,8 +1077,8 @@
       <c r="C49" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D49" s="2">
-        <v>33.932000000000002</v>
+      <c r="D49" s="1">
+        <v>33.911999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1091,8 +1091,8 @@
       <c r="C50" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D50" s="2">
-        <v>12.611000000000001</v>
+      <c r="D50" s="1">
+        <v>12.569000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D53" s="2">
         <f>D83+50</f>
-        <v>84.2</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1281,8 +1281,8 @@
       <c r="C64" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D64" s="2">
-        <v>33.932000000000002</v>
+      <c r="D64" s="1">
+        <v>33.911999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1295,8 +1295,8 @@
       <c r="C65" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="2">
-        <v>12.611000000000001</v>
+      <c r="D65" s="1">
+        <v>12.569000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D68" s="2">
         <f>D83+25</f>
-        <v>59.2</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,8 +1485,8 @@
       <c r="C79" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D79" s="2">
-        <v>33.932000000000002</v>
+      <c r="D79" s="1">
+        <v>33.911999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,8 +1499,8 @@
       <c r="C80" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D80" s="2">
-        <v>12.611000000000001</v>
+      <c r="D80" s="1">
+        <v>12.569000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1542,8 +1542,8 @@
         <v>6</v>
       </c>
       <c r="D83" s="2">
-        <f>100-65.8</f>
-        <v>34.200000000000003</v>
+        <f>100-31.8-25</f>
+        <v>43.2</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -1585,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="D86" s="2">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">

--- a/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_lemon.xlsx
+++ b/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_poincare_lemon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\Poincare beams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261782C9-1244-478C-87A5-B741236249AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA53E9A-1A82-4908-B400-430BF5D3A036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20400" yWindow="6690" windowWidth="7485" windowHeight="8670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2205" windowWidth="13350" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -449,7 +449,7 @@
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>10.66666666666667</v>
       </c>
     </row>
@@ -463,7 +463,7 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>12.77777777777778</v>
       </c>
     </row>
@@ -478,7 +478,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>33.911999999999999</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -492,7 +492,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1">
-        <v>12.569000000000001</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -651,7 +651,7 @@
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="2">
         <v>10.66666666666667</v>
       </c>
     </row>
@@ -665,7 +665,7 @@
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="2">
         <v>12.77777777777778</v>
       </c>
     </row>
@@ -680,7 +680,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>33.911999999999999</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -694,7 +694,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>12.569000000000001</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -853,7 +853,7 @@
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="2">
         <v>10.66666666666667</v>
       </c>
     </row>
@@ -867,7 +867,7 @@
       <c r="C33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="2">
         <v>12.77777777777778</v>
       </c>
     </row>
@@ -882,7 +882,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1">
-        <v>33.911999999999999</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -896,7 +896,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="1">
-        <v>12.569000000000001</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="1">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1078,7 +1078,7 @@
         <v>3</v>
       </c>
       <c r="D49" s="1">
-        <v>33.911999999999999</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1092,7 +1092,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="1">
-        <v>12.569000000000001</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D53" s="2">
         <f>D83+50</f>
-        <v>93.2</v>
+        <v>146.80000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1282,7 +1282,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="1">
-        <v>33.911999999999999</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1296,7 +1296,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="1">
-        <v>12.569000000000001</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D68" s="2">
         <f>D83+25</f>
-        <v>68.2</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1486,7 +1486,7 @@
         <v>3</v>
       </c>
       <c r="D79" s="1">
-        <v>33.911999999999999</v>
+        <v>34.472000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1500,7 +1500,7 @@
         <v>4</v>
       </c>
       <c r="D80" s="1">
-        <v>12.569000000000001</v>
+        <v>12.542999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1542,8 +1542,7 @@
         <v>6</v>
       </c>
       <c r="D83" s="2">
-        <f>100-31.8-25</f>
-        <v>43.2</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -1585,7 +1584,7 @@
         <v>8</v>
       </c>
       <c r="D86" s="2">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
